--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,85 +34,115 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_012</t>
+    <t>TC_AUTH_008</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Authentication Verification - Case 12</t>
+    <t>Authentication Verification - Case 8</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 7</t>
+  </si>
+  <si>
+    <t>TC_NAV_006</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 6</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 11</t>
-  </si>
-  <si>
-    <t>TC_FORM_017</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 17</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 176</t>
-  </si>
-  <si>
-    <t>TC_FORM_024</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 24</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 183</t>
-  </si>
-  <si>
-    <t>TC_VAL_009</t>
+    <t>AssertionError: State mismatch on scenario index 115</t>
+  </si>
+  <si>
+    <t>TC_NAV_007</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 7</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 116</t>
+  </si>
+  <si>
+    <t>TC_CRUD_032</t>
+  </si>
+  <si>
+    <t>CRUD Operations</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 32</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 231</t>
+  </si>
+  <si>
+    <t>TC_CRUD_036</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 36</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 235</t>
+  </si>
+  <si>
+    <t>TC_VAL_025</t>
   </si>
   <si>
     <t>Input Validation</t>
   </si>
   <si>
-    <t>Input Validation Verification - Case 9</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 288</t>
-  </si>
-  <si>
-    <t>TC_ERR_013</t>
+    <t>Input Validation Verification - Case 25</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 304</t>
+  </si>
+  <si>
+    <t>TC_ERR_011</t>
   </si>
   <si>
     <t>Error Handling</t>
   </si>
   <si>
-    <t>Error Handling Verification - Case 13</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 332</t>
-  </si>
-  <si>
-    <t>TC_UPL_011</t>
-  </si>
-  <si>
-    <t>File Upload</t>
-  </si>
-  <si>
-    <t>File Upload Verification - Case 11</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 390</t>
+    <t>Error Handling Verification - Case 11</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 330</t>
+  </si>
+  <si>
+    <t>TC_ERR_014</t>
+  </si>
+  <si>
+    <t>Error Handling Verification - Case 14</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 333</t>
+  </si>
+  <si>
+    <t>TC_REGR_050</t>
+  </si>
+  <si>
+    <t>Regression Suite</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 50</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 509</t>
   </si>
 </sst>
 </file>
@@ -503,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -554,7 +584,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -577,7 +607,7 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -594,27 +624,27 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -623,56 +653,125 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>295</v>
+        <v>212</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>267</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>130</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>285</v>
-      </c>
-      <c r="G7" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>289</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>132</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,13 +34,13 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_008</t>
+    <t>TC_AUTH_011</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Authentication Verification - Case 8</t>
+    <t>Authentication Verification - Case 11</t>
   </si>
   <si>
     <t>Low</t>
@@ -49,100 +49,46 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 7</t>
-  </si>
-  <si>
-    <t>TC_NAV_006</t>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 6</t>
+    <t>AssertionError: State mismatch on scenario index 10</t>
+  </si>
+  <si>
+    <t>TC_VAL_035</t>
+  </si>
+  <si>
+    <t>Input Validation</t>
+  </si>
+  <si>
+    <t>Input Validation Verification - Case 35</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 314</t>
+  </si>
+  <si>
+    <t>TC_PERF_003</t>
+  </si>
+  <si>
+    <t>Performance Smoke Tests</t>
+  </si>
+  <si>
+    <t>Performance Smoke Tests Verification - Case 3</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 115</t>
-  </si>
-  <si>
-    <t>TC_NAV_007</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 7</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 116</t>
-  </si>
-  <si>
-    <t>TC_CRUD_032</t>
-  </si>
-  <si>
-    <t>CRUD Operations</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 32</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 231</t>
-  </si>
-  <si>
-    <t>TC_CRUD_036</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 36</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 235</t>
-  </si>
-  <si>
-    <t>TC_VAL_025</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>Input Validation Verification - Case 25</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 304</t>
-  </si>
-  <si>
-    <t>TC_ERR_011</t>
-  </si>
-  <si>
-    <t>Error Handling</t>
-  </si>
-  <si>
-    <t>Error Handling Verification - Case 11</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 330</t>
-  </si>
-  <si>
-    <t>TC_ERR_014</t>
-  </si>
-  <si>
-    <t>Error Handling Verification - Case 14</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 333</t>
-  </si>
-  <si>
-    <t>TC_REGR_050</t>
+    <t>AssertionError: State mismatch on scenario index 442</t>
+  </si>
+  <si>
+    <t>TC_REGR_042</t>
   </si>
   <si>
     <t>Regression Suite</t>
   </si>
   <si>
-    <t>Regression Suite Verification - Case 50</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 509</t>
+    <t>Regression Suite Verification - Case 42</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 501</t>
   </si>
 </sst>
 </file>
@@ -533,11 +479,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -584,7 +530,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>108</v>
+        <v>238</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -601,24 +547,24 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -630,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -647,131 +593,16 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>212</v>
+        <v>119</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>267</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>174</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>103</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>289</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>132</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,61 +34,115 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_011</t>
+    <t>TC_AUTH_006</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Authentication Verification - Case 11</t>
+    <t>Authentication Verification - Case 6</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 5</t>
+  </si>
+  <si>
+    <t>TC_AUTH_026</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 26</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 10</t>
-  </si>
-  <si>
-    <t>TC_VAL_035</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>Input Validation Verification - Case 35</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 314</t>
-  </si>
-  <si>
-    <t>TC_PERF_003</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests Verification - Case 3</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 442</t>
-  </si>
-  <si>
-    <t>TC_REGR_042</t>
+    <t>AssertionError: State mismatch on scenario index 25</t>
+  </si>
+  <si>
+    <t>TC_NAV_004</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 4</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 113</t>
+  </si>
+  <si>
+    <t>TC_CRUD_028</t>
+  </si>
+  <si>
+    <t>CRUD Operations</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 28</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 227</t>
+  </si>
+  <si>
+    <t>TC_SRCH_008</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 8</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 247</t>
+  </si>
+  <si>
+    <t>TC_ACC_010</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 10</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 419</t>
+  </si>
+  <si>
+    <t>TC_REGR_018</t>
   </si>
   <si>
     <t>Regression Suite</t>
   </si>
   <si>
-    <t>Regression Suite Verification - Case 42</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 501</t>
+    <t>Regression Suite Verification - Case 18</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 477</t>
+  </si>
+  <si>
+    <t>TC_REGR_020</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 20</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 479</t>
+  </si>
+  <si>
+    <t>TC_REGR_048</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 48</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 507</t>
   </si>
 </sst>
 </file>
@@ -479,11 +533,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -530,7 +584,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -541,19 +595,19 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>294</v>
+        <v>138</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -576,7 +630,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -599,10 +653,125 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>119</v>
+        <v>256</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>217</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>166</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>245</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>134</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,115 +34,97 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_006</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Authentication Verification - Case 6</t>
+    <t>TC_PROF_019</t>
+  </si>
+  <si>
+    <t>Profile Management</t>
+  </si>
+  <si>
+    <t>Profile Management Verification - Case 19</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 108</t>
+  </si>
+  <si>
+    <t>TC_FORM_016</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Forms Verification - Case 16</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 175</t>
+  </si>
+  <si>
+    <t>TC_CRUD_003</t>
+  </si>
+  <si>
+    <t>CRUD Operations</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 3</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 5</t>
-  </si>
-  <si>
-    <t>TC_AUTH_026</t>
-  </si>
-  <si>
-    <t>Authentication Verification - Case 26</t>
+    <t>AssertionError: State mismatch on scenario index 202</t>
+  </si>
+  <si>
+    <t>TC_CRUD_019</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 19</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 218</t>
+  </si>
+  <si>
+    <t>TC_SRCH_009</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 9</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 248</t>
+  </si>
+  <si>
+    <t>TC_FILT_009</t>
+  </si>
+  <si>
+    <t>Filters</t>
+  </si>
+  <si>
+    <t>Filters Verification - Case 9</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 268</t>
+  </si>
+  <si>
+    <t>TC_ACC_014</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 14</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 25</t>
-  </si>
-  <si>
-    <t>TC_NAV_004</t>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 4</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 113</t>
-  </si>
-  <si>
-    <t>TC_CRUD_028</t>
-  </si>
-  <si>
-    <t>CRUD Operations</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 28</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 227</t>
-  </si>
-  <si>
-    <t>TC_SRCH_008</t>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 8</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 247</t>
-  </si>
-  <si>
-    <t>TC_ACC_010</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Accessibility Verification - Case 10</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 419</t>
-  </si>
-  <si>
-    <t>TC_REGR_018</t>
-  </si>
-  <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 18</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 477</t>
-  </si>
-  <si>
-    <t>TC_REGR_020</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 20</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 479</t>
-  </si>
-  <si>
-    <t>TC_REGR_048</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 48</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 507</t>
+    <t>AssertionError: State mismatch on scenario index 423</t>
   </si>
 </sst>
 </file>
@@ -533,11 +515,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -584,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -595,19 +577,19 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -630,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -641,56 +623,56 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -699,79 +681,33 @@
         <v>11</v>
       </c>
       <c r="F7">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="G8" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9">
-        <v>134</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>123</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
